--- a/data-manipulation-scripts/sheets-cleanup/sheets/CHAVE IGNIÇÃO - 29_01.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/CHAVE IGNIÇÃO - 29_01.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="105">
   <si>
     <t>CÓD. BARRA</t>
   </si>
@@ -326,72 +326,6 @@
   </si>
   <si>
     <t>CHAVE IGNIÇÃO SOLIDEZ TITAN CG125 2002 A 2004 KS 21050</t>
-  </si>
-  <si>
-    <t>7908073710464</t>
-  </si>
-  <si>
-    <t>TAMPA TANQUE SMARTFOX TITAN FAN160/ CB250F TWISTER 2016</t>
-  </si>
-  <si>
-    <t>7895099120189</t>
-  </si>
-  <si>
-    <t>TAMPA TANQUE IRON YBR125 2005 A 2007/ XTZ125 2002 A 2016/ FACTOR125/ FAZER 2013 A 2019/ XTZ250 027463</t>
-  </si>
-  <si>
-    <t>7908073725741</t>
-  </si>
-  <si>
-    <t>TAMPA TANQUE SMARTFOX XTZ150 2014</t>
-  </si>
-  <si>
-    <t>7895099122473</t>
-  </si>
-  <si>
-    <t>TAMPA TANQUE IRON BIZ125 2009/ FAN125 2009 028358</t>
-  </si>
-  <si>
-    <t>602883766563</t>
-  </si>
-  <si>
-    <t>CI IRON JET50 2014 017741</t>
-  </si>
-  <si>
-    <t>3905000018314</t>
-  </si>
-  <si>
-    <t>TAMPA TANQUE SOLIDEZ C100 DREAM 1990 A 1997 39050</t>
-  </si>
-  <si>
-    <t>39001</t>
-  </si>
-  <si>
-    <t>TAMPA TANQUE SOLIDEZ JET50 2014</t>
-  </si>
-  <si>
-    <t>6974288493394</t>
-  </si>
-  <si>
-    <t>TAMPA TANQUE BRAVIC NXR160/ FAN125/ XRE190/ XRE300 BMA63004</t>
-  </si>
-  <si>
-    <t>7895099122237</t>
-  </si>
-  <si>
-    <t>TAMPA TANQUE IRON CB300 2012 A 2021/ XRE300 2009 A 2012/ TITAN CG 2004 A 2008/ FAN150 START/ FALCON/ CBX250 027462</t>
-  </si>
-  <si>
-    <t>7898751860904</t>
-  </si>
-  <si>
-    <t>TAMPA TANQUE EXTREMO BIZ125 2011/ BIZ100 2013</t>
-  </si>
-  <si>
-    <t>6942234809162</t>
-  </si>
-  <si>
-    <t>TAMPA TANQUE BRAVIC YES125 BMA 63010</t>
   </si>
 </sst>
 </file>
@@ -1378,150 +1312,68 @@
       <c r="D53" s="3"/>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C54" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D54" s="2">
-        <v>60.0</v>
-      </c>
+      <c r="A54" s="4"/>
+      <c r="B54" s="3"/>
+      <c r="C54" s="3"/>
+      <c r="D54" s="3"/>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="C55" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="D55" s="2">
-        <v>52.0</v>
-      </c>
+      <c r="A55" s="4"/>
+      <c r="B55" s="3"/>
+      <c r="C55" s="3"/>
+      <c r="D55" s="3"/>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="C56" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="D56" s="2">
-        <v>55.0</v>
-      </c>
+      <c r="A56" s="4"/>
+      <c r="B56" s="3"/>
+      <c r="C56" s="3"/>
+      <c r="D56" s="3"/>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C57" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="D57" s="2">
-        <v>38.0</v>
-      </c>
+      <c r="A57" s="4"/>
+      <c r="B57" s="3"/>
+      <c r="C57" s="3"/>
+      <c r="D57" s="3"/>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="C58" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="D58" s="2">
-        <v>48.0</v>
-      </c>
+      <c r="A58" s="4"/>
+      <c r="B58" s="3"/>
+      <c r="C58" s="3"/>
+      <c r="D58" s="3"/>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C59" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="A59" s="4"/>
+      <c r="B59" s="3"/>
+      <c r="C59" s="3"/>
       <c r="D59" s="3"/>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C60" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D60" s="2">
-        <v>70.0</v>
-      </c>
+      <c r="A60" s="4"/>
+      <c r="B60" s="3"/>
+      <c r="C60" s="3"/>
+      <c r="D60" s="3"/>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C61" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="D61" s="2">
-        <v>80.0</v>
-      </c>
+      <c r="A61" s="4"/>
+      <c r="B61" s="3"/>
+      <c r="C61" s="3"/>
+      <c r="D61" s="3"/>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="C62" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D62" s="2">
-        <v>55.0</v>
-      </c>
+      <c r="A62" s="4"/>
+      <c r="B62" s="3"/>
+      <c r="C62" s="3"/>
+      <c r="D62" s="3"/>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="C63" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D63" s="2">
-        <v>35.0</v>
-      </c>
+      <c r="A63" s="4"/>
+      <c r="B63" s="3"/>
+      <c r="C63" s="3"/>
+      <c r="D63" s="3"/>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>126</v>
-      </c>
+      <c r="A64" s="4"/>
+      <c r="B64" s="3"/>
       <c r="C64" s="3"/>
       <c r="D64" s="3"/>
     </row>
@@ -7069,80 +6921,14 @@
       <c r="C988" s="3"/>
       <c r="D988" s="3"/>
     </row>
-    <row r="989">
-      <c r="A989" s="4"/>
-      <c r="B989" s="3"/>
-      <c r="C989" s="3"/>
-      <c r="D989" s="3"/>
-    </row>
-    <row r="990">
-      <c r="A990" s="4"/>
-      <c r="B990" s="3"/>
-      <c r="C990" s="3"/>
-      <c r="D990" s="3"/>
-    </row>
-    <row r="991">
-      <c r="A991" s="4"/>
-      <c r="B991" s="3"/>
-      <c r="C991" s="3"/>
-      <c r="D991" s="3"/>
-    </row>
-    <row r="992">
-      <c r="A992" s="4"/>
-      <c r="B992" s="3"/>
-      <c r="C992" s="3"/>
-      <c r="D992" s="3"/>
-    </row>
-    <row r="993">
-      <c r="A993" s="4"/>
-      <c r="B993" s="3"/>
-      <c r="C993" s="3"/>
-      <c r="D993" s="3"/>
-    </row>
-    <row r="994">
-      <c r="A994" s="4"/>
-      <c r="B994" s="3"/>
-      <c r="C994" s="3"/>
-      <c r="D994" s="3"/>
-    </row>
-    <row r="995">
-      <c r="A995" s="4"/>
-      <c r="B995" s="3"/>
-      <c r="C995" s="3"/>
-      <c r="D995" s="3"/>
-    </row>
-    <row r="996">
-      <c r="A996" s="4"/>
-      <c r="B996" s="3"/>
-      <c r="C996" s="3"/>
-      <c r="D996" s="3"/>
-    </row>
-    <row r="997">
-      <c r="A997" s="4"/>
-      <c r="B997" s="3"/>
-      <c r="C997" s="3"/>
-      <c r="D997" s="3"/>
-    </row>
-    <row r="998">
-      <c r="A998" s="4"/>
-      <c r="B998" s="3"/>
-      <c r="C998" s="3"/>
-      <c r="D998" s="3"/>
-    </row>
-    <row r="999">
-      <c r="A999" s="4"/>
-      <c r="B999" s="3"/>
-      <c r="C999" s="3"/>
-      <c r="D999" s="3"/>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:A999">
+  <conditionalFormatting sqref="A1:A988">
     <cfRule type="notContainsBlanks" dxfId="0" priority="1">
       <formula>LEN(TRIM(A1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A1:A999">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A1:A988">
       <formula1>COUNTIF($A:$A,A1)=1</formula1>
     </dataValidation>
   </dataValidations>
